--- a/output/Campus FY 2025-26 annual statistics NZ-level report/2025 - 2026/exclusions tab/UCSC_targeted_review_FY2025-26_exclusions_documentation_as_of_2026-07-09.xlsx
+++ b/output/Campus FY 2025-26 annual statistics NZ-level report/2025 - 2026/exclusions tab/UCSC_targeted_review_FY2025-26_exclusions_documentation_as_of_2026-07-09.xlsx
@@ -3634,7 +3634,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="55">
       <c r="A55" s="32" t="inlineStr">
         <is>
-          <t>"Portfolio Library Unit"."Library Name" is equal to / is in X_Do_Not_Use_</t>
+          <t>"Portfolio Library Unit"."Library Name" LIKE 'X_Do_Not_Use_%'</t>
         </is>
       </c>
       <c r="B55" s="39" t="inlineStr">
@@ -5711,7 +5711,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="86">
       <c r="A86" s="32" t="inlineStr">
         <is>
-          <t>"Electronic Collection"."Electronic Collection Public Name" is equal to / is in Ebook Central Perpetual, DDA and Subscription Titles; EBSCO (UCSD). eBook Collection DDA online monographs.; R2 Digital Library DDA</t>
+          <t>"Electronic Collection"."Electronic Collection Public Name" IN ('Ebook Central Perpetual, DDA and Subscription Titles', 'EBSCO (UCSD). eBook Collection DDA online monographs.', 'R2 Digital Library DDA')</t>
         </is>
       </c>
       <c r="B86" s="39" t="inlineStr">
@@ -5778,7 +5778,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="87">
       <c r="A87" s="32" t="inlineStr">
         <is>
-          <t>"Electronic Collection"."Electronic Collection Public Name" is equal to / is in British and Irish Women's Letters and Diaries: First Edition (Pre-January 2009 Purchasers Only); Books@Ovid - LWW JBIB Book Collection 2017-2018 Purchase; Books@Ovid Purchase; Books@Ovid Purchase Complete; North American Indian Drama: First Edition (Pre-October 2012 Purchasers Only); Twentieth Century North American Drama: First Edition (Pre-October 2012 Purchasers Only); Institute of Physics Historic Archive Purchase; Maruzen eBook Library; Berkeley LDC purchases; IGI Global Evidence Based PURCHASED; Oxford University Press Anthropology Local Purchased Collection; Sage EBS; Sage online monographs EBS (Sage EBS) purchased; UC Davis locally purchased monographs_LOCAL; UCSC owned streaming video; African Writers Series (pre-September 2011 purchase); SAGE Complete Deep Backfile Purchase 2008; SAGE Deep Backfile Upgrade Purchase 2009; SAGE Deep Backfile Upgrade Purchase 2010; SAGE Deep Backfile Upgrade Purchase 2011; SAGE Deep Backfile Upgrade Purchase 2012; SAGE Deep Backfile Upgrade Purchase 2013; SAGE Deep Backfile Upgrade Purchase 2014; SAGE Deep Backfile Upgrade Purchase 2015; SAGE Deep Backfile Upgrade Purchase 2016; SAGE Deep Backfile Upgrade Purchase 2017; SAGE Psychology Subject Collection Backfile Purchase; Taylor &amp; Francis online monographs (EBS) purchased</t>
+          <t>"Electronic Collection"."Electronic Collection Public Name" IN ('British and Irish Women''s Letters and Diaries: First Edition (Pre-January 2009 Purchasers Only)', 'Books@Ovid - LWW JBIB Book Collection 2017-2018 Purchase', 'Books@Ovid Purchase', 'Books@Ovid Purchase Complete', 'North American Indian Drama: First Edition (Pre-October 2012 Purchasers Only)', 'Twentieth Century North American Drama: First Edition (Pre-October 2012 Purchasers Only)', 'Institute of Physics Historic Archive Purchase', 'Maruzen eBook Library', 'Berkeley LDC purchases', 'IGI Global Evidence Based PURCHASED', 'Oxford University Press Anthropology Local Purchased Collection', 'Sage EBS', 'Sage online monographs EBS (Sage EBS) purchased', 'UC Davis locally purchased monographs_LOCAL', 'UCSC owned streaming video', 'African Writers Series (pre-September 2011 purchase)', 'SAGE Complete Deep Backfile Purchase 2008', 'SAGE Deep Backfile Upgrade Purchase 2009', 'SAGE Deep Backfile Upgrade Purchase 2010', 'SAGE Deep Backfile Upgrade Purchase 2011', 'SAGE Deep Backfile Upgrade Purchase 2012', 'SAGE Deep Backfile Upgrade Purchase 2013', 'SAGE Deep Backfile Upgrade Purchase 2014', 'SAGE Deep Backfile Upgrade Purchase 2015', 'SAGE Deep Backfile Upgrade Purchase 2016', 'SAGE Deep Backfile Upgrade Purchase 2017', 'SAGE Psychology Subject Collection Backfile Purchase', 'Taylor &amp; Francis online monographs (EBS) purchased')</t>
         </is>
       </c>
       <c r="B87" s="39" t="inlineStr">
@@ -5845,7 +5845,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="88">
       <c r="A88" s="32" t="inlineStr">
         <is>
-          <t>"Electronic Collection"."Electronic Collection Public Name"</t>
+          <t>"Electronic Collection"."Electronic Collection Public Name" IS NULL</t>
         </is>
       </c>
       <c r="B88" s="39" t="inlineStr">
@@ -6448,7 +6448,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="97">
       <c r="A97" s="32" t="inlineStr">
         <is>
-          <t>"Institution"."Institution Name"4876</t>
+          <t>"Institution"."Institution Name" = 4876</t>
         </is>
       </c>
       <c r="B97" s="39" t="inlineStr">
@@ -9798,7 +9798,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="147">
       <c r="A147" s="32" t="inlineStr">
         <is>
-          <t>"Item Location at Time of Loan"."Location Code" is equal to / is in nrlf; NRLF</t>
+          <t>"Item Location at Time of Loan"."Location Code" IN ('nrlf', 'NRLF')</t>
         </is>
       </c>
       <c r="B147" s="39" t="inlineStr">
@@ -9865,7 +9865,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="148">
       <c r="A148" s="32" t="inlineStr">
         <is>
-          <t>"Item Location at Time of Loan"."Location Code" is equal to / is in mheqp; medequip; dsi; sequp</t>
+          <t>"Item Location at Time of Loan"."Location Code" IN ('mheqp', 'medequip', 'dsi', 'sequp')</t>
         </is>
       </c>
       <c r="B148" s="39" t="inlineStr">
@@ -9999,7 +9999,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="150">
       <c r="A150" s="32" t="inlineStr">
         <is>
-          <t>"Item Location at Time of Loan"."Location Code"OUT_RS_REQ</t>
+          <t>"Item Location at Time of Loan"."Location Code" = 'OUT_RS_REQ'</t>
         </is>
       </c>
       <c r="B150" s="39" t="inlineStr">
@@ -10066,7 +10066,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="151">
       <c r="A151" s="32" t="inlineStr">
         <is>
-          <t>"Item Location at Time of Loan"."Location Code" is equal to / is in mhres; medre; scres</t>
+          <t>"Item Location at Time of Loan"."Location Code" IN ('mhres', 'medre', 'scres')</t>
         </is>
       </c>
       <c r="B151" s="39" t="inlineStr">
@@ -10133,7 +10133,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="152">
       <c r="A152" s="32" t="inlineStr">
         <is>
-          <t>"Item Location at Time of Loan"."Location Code" is equal to / is in mycur; mycov; mgcal; mgus; mprot; mref; mrdsk; mrovr; mstax; mstov; mform; mfgde; spc; medcc; med; meddo; east; sgame; scpro; sread; sstax; sstov; mhmedcc; mhmed</t>
+          <t>"Item Location at Time of Loan"."Location Code" IN ('mycur', 'mycov', 'mgcal', 'mgus', 'mprot', 'mref', 'mrdsk', 'mrovr', 'mstax', 'mstov', 'mform', 'mfgde', 'spc', 'medcc', 'med', 'meddo', 'east', 'sgame', 'scpro', 'sread', 'sstax', 'sstov', 'mhmedcc', 'mhmed')</t>
         </is>
       </c>
       <c r="B152" s="39" t="inlineStr">
@@ -10334,7 +10334,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="155">
       <c r="A155" s="32" t="inlineStr">
         <is>
-          <t>"Borrower Details"."User Group"FACULTY</t>
+          <t>"Borrower Details"."User Group" = 'FACULTY'</t>
         </is>
       </c>
       <c r="B155" s="39" t="inlineStr">
@@ -10401,7 +10401,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="156">
       <c r="A156" s="32" t="inlineStr">
         <is>
-          <t>"Borrower Details"."User Group"GRADUATE</t>
+          <t>"Borrower Details"."User Group" = 'GRADUATE'</t>
         </is>
       </c>
       <c r="B156" s="39" t="inlineStr">
@@ -10468,7 +10468,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="157">
       <c r="A157" s="32" t="inlineStr">
         <is>
-          <t>"Borrower Details"."User Group"STAFF</t>
+          <t>"Borrower Details"."User Group" = 'STAFF'</t>
         </is>
       </c>
       <c r="B157" s="39" t="inlineStr">
@@ -10535,7 +10535,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="158">
       <c r="A158" s="32" t="inlineStr">
         <is>
-          <t>"Borrower Details"."User Group"UNDERGRADUATE</t>
+          <t>"Borrower Details"."User Group" = 'UNDERGRADUATE'</t>
         </is>
       </c>
       <c r="B158" s="39" t="inlineStr">
@@ -10602,7 +10602,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="159">
       <c r="A159" s="32" t="inlineStr">
         <is>
-          <t>"Borrower Details"."User Group"COURTESY</t>
+          <t>"Borrower Details"."User Group" = 'COURTESY'</t>
         </is>
       </c>
       <c r="B159" s="39" t="inlineStr">
@@ -10669,7 +10669,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="160">
       <c r="A160" s="32" t="inlineStr">
         <is>
-          <t>"Borrower Details"."User Group" is equal to / is in NETWORK; Network</t>
+          <t>"Borrower Details"."User Group" IN ('NETWORK', 'Network')</t>
         </is>
       </c>
       <c r="B160" s="39" t="inlineStr">
@@ -10736,7 +10736,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="161">
       <c r="A161" s="32" t="inlineStr">
         <is>
-          <t>"Borrower Details"."User Group"ILL LONG-TERM 3</t>
+          <t>"Borrower Details"."User Group" = 'ILL LONG-TERM 3'</t>
         </is>
       </c>
       <c r="B161" s="39" t="inlineStr">
@@ -10803,7 +10803,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="162">
       <c r="A162" s="32" t="inlineStr">
         <is>
-          <t>"Borrower Details"."User Group"</t>
+          <t>"Borrower Details"."User Group" IS NULL</t>
         </is>
       </c>
       <c r="B162" s="39" t="inlineStr">
@@ -10870,7 +10870,7 @@
     <row collapsed="0" hidden="0" outlineLevel="5" r="163">
       <c r="A163" s="32" t="inlineStr">
         <is>
-          <t>"Borrower Details"."User Group" is equal to / is in Default; EXHIBITS; ILL LONG-TERM 1; ILL LONG-TERM 2; ILL SHORT-TERM 1; ILL SHORT-TERM 2; LIBRARY 1 YEAR; MEDIA IN HOUSE</t>
+          <t>"Borrower Details"."User Group" IN ('Default', 'EXHIBITS', 'ILL LONG-TERM 1', 'ILL LONG-TERM 2', 'ILL SHORT-TERM 1', 'ILL SHORT-TERM 2', 'LIBRARY 1 YEAR', 'MEDIA IN HOUSE')</t>
         </is>
       </c>
       <c r="B163" s="39" t="inlineStr">
